--- a/backend/data/Test.xlsx
+++ b/backend/data/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="41120" windowHeight="25720"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AM" state="visible" r:id="rId4"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="11">
   <si>
     <t>AM</t>
   </si>
@@ -29,391 +29,25 @@
     <t xml:space="preserve">Lab A </t>
   </si>
   <si>
-    <t>Bhumi Panchal</t>
-  </si>
-  <si>
-    <t>Shemina Bashir</t>
-  </si>
-  <si>
-    <t>Kumkum Chauhan</t>
-  </si>
-  <si>
-    <t>Iffat Karim</t>
-  </si>
-  <si>
-    <t>Komal Davda</t>
-  </si>
-  <si>
-    <t>Mayur Panth</t>
-  </si>
-  <si>
-    <t>Samreen</t>
-  </si>
-  <si>
-    <t>Shaymaa Morshdy</t>
-  </si>
-  <si>
-    <t>Jasmeen Kaur</t>
-  </si>
-  <si>
-    <t>Sununu Hemanth</t>
-  </si>
-  <si>
-    <t>Anam Zulfiqar</t>
-  </si>
-  <si>
-    <t>Aditi Chauhan</t>
-  </si>
-  <si>
-    <t>Shubh_Youssef_OneDrive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaspreet Kaur (4) </t>
-  </si>
-  <si>
-    <t>Amit Kour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayesha Khurram </t>
-  </si>
-  <si>
-    <t>Aakruti Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aadivalavan Arumugam </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greeshma Grace </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samiya Khan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dapinder Kaur </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Madineh </t>
-  </si>
-  <si>
-    <t>Ali Noohi</t>
-  </si>
-  <si>
-    <t>Laxmi Garg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aishani Patel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prabhjot Dhillon </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Divya Arya </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roshni Patel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Divjot Kaur Banga </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neil Vora </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatema Jivanjee </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raina Badhan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yazan Al Aqtash </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priyanka Puri </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rucha Brahmankar </t>
-  </si>
-  <si>
-    <t>Shireen Sharifi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rajbir Kaur Dhunna </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shivani Arunkumar </t>
+    <t>Shubh Test</t>
   </si>
   <si>
     <t>Lab B</t>
   </si>
   <si>
-    <t xml:space="preserve">Isra Wasim </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syeda Madiha </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jagdish Patel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iryna Vanat </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nidhin Joy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hala Abdulazeez </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jithin George </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kephana Rashmi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bishoy William </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aswathy Raju </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bhumiben Dipakkumar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ridham Modi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leila Zamani </t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harsh Sunilbhai Shah </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norhan Elmaaz </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahanvi Yash Pandya </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amr Aboelenin Ahmed </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puneet Padda </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sehaj Sharma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shweta Sharma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanan Ansari </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mansiben Dudhat </t>
-  </si>
-  <si>
-    <t>Avijit Singh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suganya Mohandoss </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satinderjot Kaur </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jignesh Goti </t>
-  </si>
-  <si>
-    <t>Bena Naqi</t>
-  </si>
-  <si>
-    <t>Navreet Bajwa</t>
-  </si>
-  <si>
-    <t>Ahmed Salama</t>
-  </si>
-  <si>
-    <t>Farheen Shaikh</t>
-  </si>
-  <si>
-    <t>Ahmed Al-Shekhli</t>
-  </si>
-  <si>
     <t>Lab C</t>
-  </si>
-  <si>
-    <t>Nisha Bawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dhyey Shah </t>
-  </si>
-  <si>
-    <t>Zarah Siddiqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmeen Kaur (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmeen Kaur </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahmed Eweis </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faheemuddin </t>
-  </si>
-  <si>
-    <t>Navpreet Kaur (6)</t>
-  </si>
-  <si>
-    <t>shuubh</t>
-  </si>
-  <si>
-    <t>testestet</t>
-  </si>
-  <si>
-    <t>Shubh</t>
   </si>
   <si>
     <t>Lab E</t>
   </si>
   <si>
-    <t>Rafik</t>
-  </si>
-  <si>
-    <t>Tamish Behal</t>
-  </si>
-  <si>
-    <t>ABCD</t>
-  </si>
-  <si>
-    <t>Ambreen Pothiawala</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>Laila Bro</t>
-  </si>
-  <si>
-    <t>Laith</t>
-  </si>
-  <si>
     <t>Lab B9</t>
-  </si>
-  <si>
-    <t>Manar Askar</t>
-  </si>
-  <si>
-    <t>Mayank Mishra</t>
-  </si>
-  <si>
-    <t>Oman Kumar</t>
-  </si>
-  <si>
-    <t>Shweta Sharma</t>
-  </si>
-  <si>
-    <t>Prerana Radadiya</t>
-  </si>
-  <si>
-    <t>Parneet Saini 1702467</t>
-  </si>
-  <si>
-    <t>Parneet Saini 1702466</t>
-  </si>
-  <si>
-    <t>Riddhi Jayant Shah</t>
-  </si>
-  <si>
-    <t>Jayashalini Puttachary</t>
-  </si>
-  <si>
-    <t>Hala Abdulazeez</t>
-  </si>
-  <si>
-    <t>Ritika Sharma</t>
-  </si>
-  <si>
-    <t>Maryam Amini</t>
-  </si>
-  <si>
-    <t>Riddhi joshi</t>
-  </si>
-  <si>
-    <t>Yogin Soni</t>
-  </si>
-  <si>
-    <t>Zahra Siddiqui</t>
-  </si>
-  <si>
-    <t>Bhumita BALAR</t>
-  </si>
-  <si>
-    <t>Sepideh Esmaeili</t>
-  </si>
-  <si>
-    <t>Vaishali Porchezhiyan</t>
-  </si>
-  <si>
-    <t>Papaldeep Virk</t>
-  </si>
-  <si>
-    <t>Srimadhuri Venigalla</t>
-  </si>
-  <si>
-    <t>Niharika Dhami</t>
-  </si>
-  <si>
-    <t>Gurmail Singh</t>
-  </si>
-  <si>
-    <t>Amr Aboelenin Ahmed</t>
-  </si>
-  <si>
-    <t>Paramjit Kaur</t>
   </si>
   <si>
     <t>Lab D</t>
   </si>
   <si>
-    <t>Kirandeep Aulakh</t>
-  </si>
-  <si>
-    <t>Ridhi Shah</t>
-  </si>
-  <si>
-    <t>Harsh shah</t>
-  </si>
-  <si>
-    <t>Harsh Shah</t>
-  </si>
-  <si>
-    <t>Shweta Virani</t>
-  </si>
-  <si>
-    <t>Thuy Dan Phuong Ngo</t>
-  </si>
-  <si>
-    <t>Anuradha Deshmukh</t>
-  </si>
-  <si>
-    <t>Norhan Elmaaz</t>
-  </si>
-  <si>
-    <t>Vikramjit Singh</t>
-  </si>
-  <si>
-    <t>Tamish BEHAL</t>
-  </si>
-  <si>
     <t>PM</t>
-  </si>
-  <si>
-    <t>QAW</t>
   </si>
 </sst>
 </file>
@@ -813,20 +447,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N1000"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.7109375"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.5703125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="29.28515625" customWidth="1"/>
-    <col min="8" max="14" width="22.28515625" customWidth="1"/>
-    <col min="15" max="27" width="8.7109375" customWidth="1"/>
+    <col min="3" max="14" width="22.42578125" customWidth="1"/>
+    <col min="15" max="27" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -876,40 +505,40 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>45866</v>
+        <v>45950</v>
       </c>
       <c r="D2" s="2">
-        <v>45873</v>
+        <v>45957</v>
       </c>
       <c r="E2" s="2">
-        <v>45880</v>
+        <v>45964</v>
       </c>
       <c r="F2" s="2">
-        <v>45887</v>
+        <v>45971</v>
       </c>
       <c r="G2" s="2">
-        <v>45894</v>
+        <v>45978</v>
       </c>
       <c r="H2" s="2">
-        <v>45901</v>
+        <v>45985</v>
       </c>
       <c r="I2" s="2">
-        <v>45908</v>
+        <v>45992</v>
       </c>
       <c r="J2" s="2">
-        <v>45915</v>
+        <v>45999</v>
       </c>
       <c r="K2" s="2">
-        <v>45922</v>
+        <v>46006</v>
       </c>
       <c r="L2" s="2">
-        <v>45929</v>
+        <v>46013</v>
       </c>
       <c r="M2" s="2">
-        <v>45936</v>
+        <v>46020</v>
       </c>
       <c r="N2" s="2">
-        <v>45943</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -919,9 +548,7 @@
       <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
@@ -952,9 +579,7 @@
       <c r="M3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="N3" s="4"/>
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -963,42 +588,18 @@
       <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -1007,42 +608,18 @@
       <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -1051,42 +628,18 @@
       <c r="B6" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -1095,42 +648,18 @@
       <c r="B7" s="4">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -1139,42 +668,18 @@
       <c r="B8" s="4">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -1183,27 +688,13 @@
       <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -1217,42 +708,18 @@
       <c r="B10" s="4">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -1261,42 +728,18 @@
       <c r="B11" s="4">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -1305,42 +748,18 @@
       <c r="B12" s="4">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -1349,33 +768,15 @@
       <c r="B13" s="4">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1387,15 +788,9 @@
       <c r="B14" s="4">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -1413,42 +808,18 @@
       <c r="B15" s="4">
         <v>13</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -1457,42 +828,18 @@
       <c r="B16" s="4">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
@@ -1501,42 +848,18 @@
       <c r="B17" s="4">
         <v>15</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -1545,42 +868,18 @@
       <c r="B18" s="4">
         <v>16</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
@@ -1589,42 +888,18 @@
       <c r="B19" s="4">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -1633,42 +908,18 @@
       <c r="B20" s="4">
         <v>18</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
@@ -1677,42 +928,18 @@
       <c r="B21" s="4">
         <v>19</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
     </row>
     <row r="22" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -1721,42 +948,18 @@
       <c r="B22" s="4">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
@@ -1765,42 +968,18 @@
       <c r="B23" s="4">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
     </row>
     <row r="24" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -1809,42 +988,18 @@
       <c r="B24" s="4">
         <v>22</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
@@ -1853,42 +1008,18 @@
       <c r="B25" s="4">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
     </row>
     <row r="26" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -1897,42 +1028,18 @@
       <c r="B26" s="4">
         <v>24</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -1941,42 +1048,18 @@
       <c r="B27" s="4">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
@@ -1985,42 +1068,18 @@
       <c r="B28" s="4">
         <v>26</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
     </row>
     <row r="29" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
@@ -2029,42 +1088,18 @@
       <c r="B29" s="4">
         <v>27</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
     </row>
     <row r="30" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
@@ -2073,42 +1108,18 @@
       <c r="B30" s="4">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -2117,42 +1128,18 @@
       <c r="B31" s="4">
         <v>29</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
@@ -2161,15 +1148,9 @@
       <c r="B32" s="4">
         <v>30</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -2187,42 +1168,18 @@
       <c r="B33" s="4">
         <v>31</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="N33" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
@@ -2231,42 +1188,18 @@
       <c r="B34" s="4">
         <v>32</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -2275,42 +1208,18 @@
       <c r="B35" s="4">
         <v>33</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N35" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -2319,42 +1228,18 @@
       <c r="B36" s="4">
         <v>34</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
@@ -2363,42 +1248,18 @@
       <c r="B37" s="4">
         <v>35</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N37" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
     </row>
     <row r="38" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
@@ -2407,42 +1268,18 @@
       <c r="B38" s="4">
         <v>36</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N38" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
     </row>
     <row r="39" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2451,42 +1288,18 @@
       <c r="B39" s="4">
         <v>37</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
@@ -2495,232 +1308,108 @@
       <c r="B40" s="4">
         <v>38</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N40" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
     </row>
     <row r="41" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B41" s="5">
         <v>1</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N41" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
     </row>
     <row r="42" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B42" s="5">
         <v>2</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
     </row>
     <row r="43" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B43" s="5">
         <v>3</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B44" s="5">
         <v>4</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="N44" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B45" s="5">
         <v>5</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -2734,23 +1423,15 @@
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B46" s="5">
         <v>6</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -2762,17 +1443,13 @@
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B47" s="5">
         <v>7</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -2786,23 +1463,15 @@
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B48" s="5">
         <v>8</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -2814,23 +1483,15 @@
     </row>
     <row r="49" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B49" s="5">
         <v>9</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="11"/>
       <c r="H49" s="5"/>
       <c r="I49" s="11"/>
@@ -2842,23 +1503,15 @@
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B50" s="5">
         <v>10</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
@@ -2870,23 +1523,15 @@
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B51" s="5">
         <v>11</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
@@ -2898,23 +1543,15 @@
     </row>
     <row r="52" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B52" s="5">
         <v>12</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>54</v>
-      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
       <c r="G52" s="11"/>
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
@@ -2926,61 +1563,33 @@
     </row>
     <row r="53" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B53" s="5">
         <v>13</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M53" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N53" s="11" t="s">
-        <v>56</v>
-      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
     </row>
     <row r="54" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B54" s="5">
         <v>14</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="11"/>
@@ -2994,17 +1603,13 @@
     </row>
     <row r="55" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B55" s="5">
         <v>15</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
@@ -3018,17 +1623,13 @@
     </row>
     <row r="56" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B56" s="5">
         <v>16</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>59</v>
-      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="11"/>
@@ -3042,26 +1643,16 @@
     </row>
     <row r="57" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B57" s="5">
         <v>17</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11"/>
@@ -3072,29 +1663,17 @@
     </row>
     <row r="58" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B58" s="5">
         <v>18</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
       <c r="I58" s="11"/>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
@@ -3104,29 +1683,17 @@
     </row>
     <row r="59" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B59" s="5">
         <v>19</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
@@ -3136,29 +1703,17 @@
     </row>
     <row r="60" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B60" s="5">
         <v>20</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>63</v>
-      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
@@ -3168,20 +1723,14 @@
     </row>
     <row r="61" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B61" s="5">
         <v>21</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
       <c r="F61" s="11"/>
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
@@ -3194,23 +1743,15 @@
     </row>
     <row r="62" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B62" s="5">
         <v>22</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
@@ -3222,14 +1763,12 @@
     </row>
     <row r="63" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B63" s="5">
         <v>23</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="C63" s="5"/>
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
@@ -3244,23 +1783,15 @@
     </row>
     <row r="64" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B64" s="5">
         <v>24</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
@@ -3272,29 +1803,17 @@
     </row>
     <row r="65" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B65" s="5">
         <v>25</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
       <c r="I65" s="11"/>
       <c r="J65" s="11"/>
       <c r="K65" s="11"/>
@@ -3304,26 +1823,16 @@
     </row>
     <row r="66" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B66" s="5">
         <v>26</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
@@ -3334,26 +1843,16 @@
     </row>
     <row r="67" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B67" s="5">
         <v>27</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>70</v>
-      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
       <c r="J67" s="11"/>
@@ -3364,67 +1863,35 @@
     </row>
     <row r="68" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B68" s="5">
         <v>28</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="L68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N68" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
     </row>
     <row r="69" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B69" s="5">
         <v>29</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>72</v>
-      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
@@ -3436,26 +1903,16 @@
     </row>
     <row r="70" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B70" s="5">
         <v>30</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>73</v>
-      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
       <c r="J70" s="11"/>
@@ -3466,29 +1923,17 @@
     </row>
     <row r="71" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B71" s="5">
         <v>31</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
       <c r="I71" s="11"/>
       <c r="J71" s="11"/>
       <c r="K71" s="11"/>
@@ -3498,14 +1943,12 @@
     </row>
     <row r="72" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B72" s="5">
         <v>1</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>76</v>
-      </c>
+      <c r="C72" s="5"/>
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
@@ -3520,17 +1963,13 @@
     </row>
     <row r="73" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B73" s="5">
         <v>2</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>77</v>
-      </c>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
       <c r="G73" s="11"/>
@@ -3544,23 +1983,15 @@
     </row>
     <row r="74" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B74" s="5">
         <v>3</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
@@ -3572,14 +2003,12 @@
     </row>
     <row r="75" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B75" s="5">
         <v>4</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="C75" s="5"/>
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="11"/>
@@ -3594,14 +2023,12 @@
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B76" s="5">
         <v>5</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>80</v>
-      </c>
+      <c r="C76" s="5"/>
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="11"/>
@@ -3616,14 +2043,12 @@
     </row>
     <row r="77" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B77" s="5">
         <v>6</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="C77" s="5"/>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
       <c r="F77" s="11"/>
@@ -3638,26 +2063,16 @@
     </row>
     <row r="78" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B78" s="5">
         <v>7</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
       <c r="J78" s="11"/>
@@ -3668,14 +2083,12 @@
     </row>
     <row r="79" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B79" s="5">
         <v>8</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="C79" s="5"/>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
       <c r="F79" s="11"/>
@@ -3690,95 +2103,47 @@
     </row>
     <row r="80" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B80" s="5">
         <v>9</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="H80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="L80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="M80" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="N80" s="11" t="s">
-        <v>84</v>
-      </c>
+      <c r="C80" s="5"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="11"/>
     </row>
     <row r="81" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B81" s="5">
         <v>10</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="K81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="L81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="M81" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="N81" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="C81" s="5"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="11"/>
     </row>
     <row r="82" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B82" s="5">
         <v>11</v>
@@ -3798,7 +2163,7 @@
     </row>
     <row r="83" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B83" s="5">
         <v>12</v>
@@ -3818,28 +2183,18 @@
     </row>
     <row r="84" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B84" s="5">
         <v>13</v>
       </c>
       <c r="C84" s="5"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F84" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G84" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H84" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I84" s="11" t="s">
-        <v>86</v>
-      </c>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
       <c r="L84" s="11"/>
@@ -3848,7 +2203,7 @@
     </row>
     <row r="85" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B85" s="5">
         <v>14</v>
@@ -3868,32 +2223,18 @@
     </row>
     <row r="86" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B86" s="5">
         <v>1</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D86" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="F86" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G86" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H86" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I86" s="11" t="s">
-        <v>88</v>
-      </c>
+      <c r="C86" s="5"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
       <c r="J86" s="11"/>
       <c r="K86" s="11"/>
       <c r="L86" s="11"/>
@@ -3902,32 +2243,18 @@
     </row>
     <row r="87" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B87" s="5">
         <v>2</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F87" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="G87" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="H87" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I87" s="11" t="s">
-        <v>89</v>
-      </c>
+      <c r="C87" s="5"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
       <c r="L87" s="11"/>
@@ -3936,32 +2263,18 @@
     </row>
     <row r="88" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B88" s="5">
         <v>3</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="H88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="I88" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="C88" s="5"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
       <c r="J88" s="11"/>
       <c r="K88" s="11"/>
       <c r="L88" s="11"/>
@@ -3970,32 +2283,18 @@
     </row>
     <row r="89" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B89" s="5">
         <v>4</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G89" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="H89" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="I89" s="11" t="s">
-        <v>91</v>
-      </c>
+      <c r="C89" s="5"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
       <c r="L89" s="11"/>
@@ -4004,32 +2303,18 @@
     </row>
     <row r="90" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B90" s="5">
         <v>5</v>
       </c>
-      <c r="C90" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F90" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G90" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I90" s="11" t="s">
-        <v>92</v>
-      </c>
+      <c r="C90" s="5"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
       <c r="L90" s="11"/>
@@ -4038,7 +2323,7 @@
     </row>
     <row r="91" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B91" s="5">
         <v>6</v>
@@ -4058,7 +2343,7 @@
     </row>
     <row r="92" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B92" s="5">
         <v>7</v>
@@ -4078,7 +2363,7 @@
     </row>
     <row r="93" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B93" s="5">
         <v>8</v>
@@ -4098,7 +2383,7 @@
     </row>
     <row r="94" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B94" s="5">
         <v>9</v>
@@ -4118,32 +2403,18 @@
     </row>
     <row r="95" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B95" s="5">
         <v>10</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F95" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G95" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H95" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="I95" s="11" t="s">
-        <v>93</v>
-      </c>
+      <c r="C95" s="5"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
       <c r="J95" s="11"/>
       <c r="K95" s="11"/>
       <c r="L95" s="11"/>
@@ -4152,7 +2423,7 @@
     </row>
     <row r="96" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B96" s="5">
         <v>11</v>
@@ -4172,32 +2443,18 @@
     </row>
     <row r="97" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B97" s="5">
         <v>12</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E97" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F97" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G97" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H97" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="I97" s="11" t="s">
-        <v>94</v>
-      </c>
+      <c r="C97" s="5"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11"/>
       <c r="J97" s="11"/>
       <c r="K97" s="11"/>
       <c r="L97" s="11"/>
@@ -4206,7 +2463,7 @@
     </row>
     <row r="98" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B98" s="5">
         <v>13</v>
@@ -4226,7 +2483,7 @@
     </row>
     <row r="99" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B99" s="5">
         <v>14</v>
@@ -4246,29 +2503,17 @@
     </row>
     <row r="100" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B100" s="13">
         <v>1</v>
       </c>
-      <c r="C100" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G100" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>74</v>
-      </c>
+      <c r="C100" s="14"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
+      <c r="H100" s="14"/>
       <c r="I100" s="14"/>
       <c r="J100" s="15"/>
       <c r="K100" s="14"/>
@@ -4278,20 +2523,14 @@
     </row>
     <row r="101" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B101" s="13">
         <v>2</v>
       </c>
-      <c r="C101" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D101" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E101" s="17" t="s">
-        <v>98</v>
-      </c>
+      <c r="C101" s="14"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
       <c r="F101" s="14"/>
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
@@ -4304,20 +2543,14 @@
     </row>
     <row r="102" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B102" s="13">
         <v>3</v>
       </c>
-      <c r="C102" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E102" s="14" t="s">
-        <v>99</v>
-      </c>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="14"/>
       <c r="F102" s="14"/>
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
@@ -4330,21 +2563,15 @@
     </row>
     <row r="103" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B103" s="13">
         <v>4</v>
       </c>
       <c r="C103" s="14"/>
-      <c r="D103" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F103" s="14" t="s">
-        <v>100</v>
-      </c>
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
@@ -4356,26 +2583,16 @@
     </row>
     <row r="104" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B104" s="13">
         <v>5</v>
       </c>
-      <c r="C104" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D104" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F104" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G104" s="14" t="s">
-        <v>101</v>
-      </c>
+      <c r="C104" s="14"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="14"/>
       <c r="J104" s="15"/>
@@ -4386,23 +2603,15 @@
     </row>
     <row r="105" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B105" s="13">
         <v>6</v>
       </c>
-      <c r="C105" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D105" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>97</v>
-      </c>
+      <c r="C105" s="14"/>
+      <c r="D105" s="17"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
@@ -4414,29 +2623,17 @@
     </row>
     <row r="106" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B106" s="13">
         <v>7</v>
       </c>
-      <c r="C106" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E106" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F106" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G106" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H106" s="14" t="s">
-        <v>105</v>
-      </c>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14"/>
       <c r="I106" s="14"/>
       <c r="J106" s="15"/>
       <c r="K106" s="14"/>
@@ -4446,17 +2643,13 @@
     </row>
     <row r="107" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B107" s="13">
         <v>8</v>
       </c>
-      <c r="C107" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>106</v>
-      </c>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
       <c r="E107" s="14"/>
       <c r="F107" s="14"/>
       <c r="G107" s="14"/>
@@ -4470,17 +2663,13 @@
     </row>
     <row r="108" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B108" s="13">
         <v>9</v>
       </c>
-      <c r="C108" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>107</v>
-      </c>
+      <c r="C108" s="14"/>
+      <c r="D108" s="14"/>
       <c r="E108" s="14"/>
       <c r="F108" s="14"/>
       <c r="G108" s="14"/>
@@ -4494,18 +2683,14 @@
     </row>
     <row r="109" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B109" s="13">
         <v>10</v>
       </c>
       <c r="C109" s="14"/>
-      <c r="D109" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>109</v>
-      </c>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
       <c r="F109" s="14"/>
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
@@ -4518,29 +2703,17 @@
     </row>
     <row r="110" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B110" s="13">
         <v>11</v>
       </c>
-      <c r="C110" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D110" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E110" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F110" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="G110" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H110" s="14" t="s">
-        <v>110</v>
-      </c>
+      <c r="C110" s="14"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
+      <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="15"/>
       <c r="K110" s="14"/>
@@ -4550,26 +2723,16 @@
     </row>
     <row r="111" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B111" s="13">
         <v>12</v>
       </c>
-      <c r="C111" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E111" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F111" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G111" s="14" t="s">
-        <v>108</v>
-      </c>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="14"/>
       <c r="J111" s="15"/>
@@ -4580,23 +2743,15 @@
     </row>
     <row r="112" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B112" s="13">
         <v>13</v>
       </c>
-      <c r="C112" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D112" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E112" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F112" s="17" t="s">
-        <v>112</v>
-      </c>
+      <c r="C112" s="17"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="17"/>
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="17"/>
@@ -4608,20 +2763,14 @@
     </row>
     <row r="113" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B113" s="13">
         <v>14</v>
       </c>
-      <c r="C113" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D113" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E113" s="14" t="s">
-        <v>113</v>
-      </c>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
       <c r="F113" s="14"/>
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
@@ -4634,17 +2783,13 @@
     </row>
     <row r="114" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B114" s="13">
         <v>15</v>
       </c>
-      <c r="C114" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D114" s="14" t="s">
-        <v>114</v>
-      </c>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
       <c r="E114" s="14"/>
       <c r="F114" s="14"/>
       <c r="G114" s="14"/>
@@ -4658,20 +2803,14 @@
     </row>
     <row r="115" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B115" s="13">
         <v>16</v>
       </c>
-      <c r="C115" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E115" s="14" t="s">
-        <v>115</v>
-      </c>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
       <c r="F115" s="18"/>
       <c r="G115" s="18"/>
       <c r="H115" s="18"/>
@@ -4684,20 +2823,14 @@
     </row>
     <row r="116" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B116" s="13">
         <v>17</v>
       </c>
-      <c r="C116" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D116" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E116" s="14" t="s">
-        <v>116</v>
-      </c>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
       <c r="F116" s="18"/>
       <c r="G116" s="18"/>
       <c r="H116" s="18"/>
@@ -4710,20 +2843,14 @@
     </row>
     <row r="117" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B117" s="13">
         <v>18</v>
       </c>
-      <c r="C117" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="D117" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E117" s="19" t="s">
-        <v>117</v>
-      </c>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
       <c r="F117" s="14"/>
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
@@ -4736,26 +2863,16 @@
     </row>
     <row r="118" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B118" s="13">
         <v>19</v>
       </c>
-      <c r="C118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="G118" s="14" t="s">
-        <v>118</v>
-      </c>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
       <c r="H118" s="18"/>
       <c r="I118" s="14"/>
       <c r="J118" s="15"/>
@@ -4766,29 +2883,17 @@
     </row>
     <row r="119" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B119" s="13">
         <v>20</v>
       </c>
-      <c r="C119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H119" s="14" t="s">
-        <v>119</v>
-      </c>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
       <c r="I119" s="14"/>
       <c r="J119" s="15"/>
       <c r="K119" s="14"/>
@@ -4798,17 +2903,13 @@
     </row>
     <row r="120" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B120" s="7">
         <v>1</v>
       </c>
-      <c r="C120" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>121</v>
-      </c>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
       <c r="E120" s="16"/>
       <c r="F120" s="16"/>
       <c r="G120" s="16"/>
@@ -4822,20 +2923,14 @@
     </row>
     <row r="121" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B121" s="20">
         <v>2</v>
       </c>
-      <c r="C121" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D121" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E121" s="20" t="s">
-        <v>122</v>
-      </c>
+      <c r="C121" s="20"/>
+      <c r="D121" s="20"/>
+      <c r="E121" s="20"/>
       <c r="F121" s="14"/>
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
@@ -4848,17 +2943,13 @@
     </row>
     <row r="122" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B122" s="7">
         <v>3</v>
       </c>
-      <c r="C122" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D122" s="18" t="s">
-        <v>124</v>
-      </c>
+      <c r="C122" s="18"/>
+      <c r="D122" s="18"/>
       <c r="E122" s="14"/>
       <c r="F122" s="14"/>
       <c r="G122" s="14"/>
@@ -4872,20 +2963,14 @@
     </row>
     <row r="123" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B123" s="20">
         <v>4</v>
       </c>
-      <c r="C123" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>125</v>
-      </c>
+      <c r="C123" s="14"/>
+      <c r="D123" s="14"/>
+      <c r="E123" s="14"/>
       <c r="F123" s="14"/>
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
@@ -4898,20 +2983,14 @@
     </row>
     <row r="124" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B124" s="7">
         <v>5</v>
       </c>
-      <c r="C124" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>116</v>
-      </c>
+      <c r="C124" s="14"/>
+      <c r="D124" s="14"/>
+      <c r="E124" s="14"/>
       <c r="F124" s="14"/>
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
@@ -4924,17 +3003,13 @@
     </row>
     <row r="125" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B125" s="20">
         <v>6</v>
       </c>
-      <c r="C125" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D125" s="14" t="s">
-        <v>126</v>
-      </c>
+      <c r="C125" s="14"/>
+      <c r="D125" s="14"/>
       <c r="E125" s="14"/>
       <c r="F125" s="14"/>
       <c r="G125" s="14"/>
@@ -4948,7 +3023,7 @@
     </row>
     <row r="126" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B126" s="7">
         <v>7</v>
@@ -4968,7 +3043,7 @@
     </row>
     <row r="127" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B127" s="20">
         <v>8</v>
@@ -4988,17 +3063,13 @@
     </row>
     <row r="128" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B128" s="7">
         <v>9</v>
       </c>
-      <c r="C128" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D128" s="21" t="s">
-        <v>127</v>
-      </c>
+      <c r="C128" s="14"/>
+      <c r="D128" s="21"/>
       <c r="E128" s="14"/>
       <c r="F128" s="14"/>
       <c r="G128" s="14"/>
@@ -5012,7 +3083,7 @@
     </row>
     <row r="129" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B129" s="20">
         <v>10</v>
@@ -5032,16 +3103,14 @@
     </row>
     <row r="130" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B130" s="7">
         <v>11</v>
       </c>
       <c r="C130" s="22"/>
       <c r="D130" s="22"/>
-      <c r="E130" s="14" t="s">
-        <v>128</v>
-      </c>
+      <c r="E130" s="14"/>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
@@ -5054,7 +3123,7 @@
     </row>
     <row r="131" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B131" s="20">
         <v>12</v>
@@ -5074,7 +3143,7 @@
     </row>
     <row r="132" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B132" s="7">
         <v>13</v>
@@ -5094,7 +3163,7 @@
     </row>
     <row r="133" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B133" s="20">
         <v>14</v>
@@ -5114,14 +3183,12 @@
     </row>
     <row r="134" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B134" s="7">
         <v>15</v>
       </c>
-      <c r="C134" s="23" t="s">
-        <v>129</v>
-      </c>
+      <c r="C134" s="23"/>
       <c r="D134" s="14"/>
       <c r="E134" s="14"/>
       <c r="F134" s="14"/>
@@ -5131,12 +3198,8 @@
       <c r="J134" s="14"/>
       <c r="K134" s="14"/>
       <c r="L134" s="14"/>
-      <c r="M134" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="N134" s="14" t="s">
-        <v>130</v>
-      </c>
+      <c r="M134" s="14"/>
+      <c r="N134" s="14"/>
     </row>
     <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6013,17 +4076,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N1000"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.7109375"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.5703125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" customWidth="1"/>
-    <col min="3" max="14" width="22.28515625" customWidth="1"/>
-    <col min="15" max="27" width="8.7109375" customWidth="1"/>
+    <col min="3" max="14" width="22.42578125" customWidth="1"/>
+    <col min="15" max="27" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1">
@@ -6063,7 +4126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6071,40 +4134,40 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>45866</v>
+        <v>45950</v>
       </c>
       <c r="D2" s="2">
-        <v>45873</v>
+        <v>45957</v>
       </c>
       <c r="E2" s="2">
-        <v>45880</v>
+        <v>45964</v>
       </c>
       <c r="F2" s="2">
-        <v>45887</v>
+        <v>45971</v>
       </c>
       <c r="G2" s="2">
-        <v>45894</v>
+        <v>45978</v>
       </c>
       <c r="H2" s="2">
-        <v>45901</v>
+        <v>45985</v>
       </c>
       <c r="I2" s="2">
-        <v>45908</v>
+        <v>45992</v>
       </c>
       <c r="J2" s="2">
-        <v>45915</v>
+        <v>45999</v>
       </c>
       <c r="K2" s="2">
-        <v>45922</v>
+        <v>46006</v>
       </c>
       <c r="L2" s="2">
-        <v>45929</v>
+        <v>46013</v>
       </c>
       <c r="M2" s="2">
-        <v>45936</v>
+        <v>46020</v>
       </c>
       <c r="N2" s="2">
-        <v>45943</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -6114,42 +4177,18 @@
       <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -6158,42 +4197,18 @@
       <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -6202,42 +4217,18 @@
       <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -6246,42 +4237,18 @@
       <c r="B6" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -6290,42 +4257,18 @@
       <c r="B7" s="4">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -6334,42 +4277,18 @@
       <c r="B8" s="4">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -6378,39 +4297,17 @@
       <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>132</v>
-      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
       <c r="N9" s="6"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -6420,42 +4317,18 @@
       <c r="B10" s="4">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -6464,42 +4337,18 @@
       <c r="B11" s="4">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -6508,42 +4357,18 @@
       <c r="B12" s="4">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -6552,33 +4377,15 @@
       <c r="B13" s="4">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -6590,15 +4397,9 @@
       <c r="B14" s="4">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -6636,42 +4437,18 @@
       <c r="B16" s="4">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
@@ -6680,42 +4457,18 @@
       <c r="B17" s="4">
         <v>15</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -6724,42 +4477,18 @@
       <c r="B18" s="4">
         <v>16</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
@@ -6768,42 +4497,18 @@
       <c r="B19" s="4">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -6812,42 +4517,18 @@
       <c r="B20" s="4">
         <v>18</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
@@ -6856,42 +4537,18 @@
       <c r="B21" s="4">
         <v>19</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
     </row>
     <row r="22" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -6900,42 +4557,18 @@
       <c r="B22" s="4">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
@@ -6944,42 +4577,18 @@
       <c r="B23" s="4">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
     </row>
     <row r="24" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -6988,42 +4597,18 @@
       <c r="B24" s="4">
         <v>22</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
@@ -7032,42 +4617,18 @@
       <c r="B25" s="4">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
     </row>
     <row r="26" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -7076,42 +4637,18 @@
       <c r="B26" s="4">
         <v>24</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -7120,42 +4657,18 @@
       <c r="B27" s="4">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
@@ -7164,42 +4677,18 @@
       <c r="B28" s="4">
         <v>26</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
     </row>
     <row r="29" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
@@ -7208,42 +4697,18 @@
       <c r="B29" s="4">
         <v>27</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
     </row>
     <row r="30" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
@@ -7252,42 +4717,18 @@
       <c r="B30" s="4">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -7296,42 +4737,18 @@
       <c r="B31" s="4">
         <v>29</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
@@ -7340,15 +4757,9 @@
       <c r="B32" s="4">
         <v>30</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -7366,42 +4777,18 @@
       <c r="B33" s="4">
         <v>31</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="N33" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
@@ -7410,42 +4797,18 @@
       <c r="B34" s="4">
         <v>32</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -7454,42 +4817,18 @@
       <c r="B35" s="4">
         <v>33</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N35" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -7498,42 +4837,18 @@
       <c r="B36" s="4">
         <v>34</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
@@ -7542,42 +4857,18 @@
       <c r="B37" s="4">
         <v>35</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N37" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
     </row>
     <row r="38" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
@@ -7586,42 +4877,18 @@
       <c r="B38" s="4">
         <v>36</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N38" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
     </row>
     <row r="39" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -7630,42 +4897,18 @@
       <c r="B39" s="4">
         <v>37</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
@@ -7674,232 +4917,108 @@
       <c r="B40" s="4">
         <v>38</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N40" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
     </row>
     <row r="41" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B41" s="5">
         <v>1</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N41" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
     </row>
     <row r="42" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B42" s="5">
         <v>2</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
     </row>
     <row r="43" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B43" s="5">
         <v>3</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B44" s="5">
         <v>4</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="N44" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B45" s="5">
         <v>5</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -7913,23 +5032,15 @@
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B46" s="5">
         <v>6</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -7941,17 +5052,13 @@
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B47" s="5">
         <v>7</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -7965,23 +5072,15 @@
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B48" s="5">
         <v>8</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -7993,23 +5092,15 @@
     </row>
     <row r="49" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B49" s="5">
         <v>9</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="11"/>
       <c r="H49" s="5"/>
       <c r="I49" s="11"/>
@@ -8021,23 +5112,15 @@
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B50" s="5">
         <v>10</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
@@ -8049,23 +5132,15 @@
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B51" s="5">
         <v>11</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
@@ -8077,23 +5152,15 @@
     </row>
     <row r="52" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B52" s="5">
         <v>12</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>54</v>
-      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
       <c r="G52" s="11"/>
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
@@ -8105,14 +5172,12 @@
     </row>
     <row r="53" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B53" s="5">
         <v>13</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
@@ -8127,17 +5192,13 @@
     </row>
     <row r="54" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B54" s="5">
         <v>14</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="11"/>
@@ -8151,17 +5212,13 @@
     </row>
     <row r="55" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B55" s="5">
         <v>15</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
@@ -8175,17 +5232,13 @@
     </row>
     <row r="56" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B56" s="5">
         <v>16</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>59</v>
-      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="11"/>
@@ -8199,26 +5252,16 @@
     </row>
     <row r="57" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B57" s="5">
         <v>17</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11"/>
@@ -8229,29 +5272,17 @@
     </row>
     <row r="58" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B58" s="5">
         <v>18</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
       <c r="I58" s="11"/>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
@@ -8261,29 +5292,17 @@
     </row>
     <row r="59" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B59" s="5">
         <v>19</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
@@ -8293,29 +5312,17 @@
     </row>
     <row r="60" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B60" s="5">
         <v>20</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>63</v>
-      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
@@ -8325,20 +5332,14 @@
     </row>
     <row r="61" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B61" s="5">
         <v>21</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
       <c r="F61" s="11"/>
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
@@ -8351,23 +5352,15 @@
     </row>
     <row r="62" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B62" s="5">
         <v>22</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
@@ -8379,14 +5372,12 @@
     </row>
     <row r="63" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B63" s="5">
         <v>23</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="C63" s="5"/>
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
@@ -8401,23 +5392,15 @@
     </row>
     <row r="64" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B64" s="5">
         <v>24</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
@@ -8429,29 +5412,17 @@
     </row>
     <row r="65" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B65" s="5">
         <v>25</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
       <c r="I65" s="11"/>
       <c r="J65" s="11"/>
       <c r="K65" s="11"/>
@@ -8461,26 +5432,16 @@
     </row>
     <row r="66" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B66" s="5">
         <v>26</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
@@ -8491,26 +5452,16 @@
     </row>
     <row r="67" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B67" s="5">
         <v>27</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>70</v>
-      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
       <c r="H67" s="11"/>
       <c r="I67" s="11"/>
       <c r="J67" s="11"/>
@@ -8521,67 +5472,35 @@
     </row>
     <row r="68" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B68" s="5">
         <v>28</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="L68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M68" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N68" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
     </row>
     <row r="69" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B69" s="5">
         <v>29</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>72</v>
-      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
@@ -8593,26 +5512,16 @@
     </row>
     <row r="70" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B70" s="5">
         <v>30</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>73</v>
-      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
       <c r="J70" s="11"/>
@@ -8623,29 +5532,17 @@
     </row>
     <row r="71" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B71" s="5">
         <v>31</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
       <c r="I71" s="11"/>
       <c r="J71" s="11"/>
       <c r="K71" s="11"/>
@@ -8655,14 +5552,12 @@
     </row>
     <row r="72" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B72" s="5">
         <v>1</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>76</v>
-      </c>
+      <c r="C72" s="5"/>
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
@@ -8677,17 +5572,13 @@
     </row>
     <row r="73" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B73" s="5">
         <v>2</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>77</v>
-      </c>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
       <c r="G73" s="11"/>
@@ -8701,23 +5592,15 @@
     </row>
     <row r="74" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B74" s="5">
         <v>3</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
@@ -8729,14 +5612,12 @@
     </row>
     <row r="75" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B75" s="5">
         <v>4</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="C75" s="5"/>
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="11"/>
@@ -8751,14 +5632,12 @@
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B76" s="5">
         <v>5</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>80</v>
-      </c>
+      <c r="C76" s="5"/>
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="11"/>
@@ -8773,14 +5652,12 @@
     </row>
     <row r="77" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B77" s="5">
         <v>6</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="C77" s="5"/>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
       <c r="F77" s="11"/>
@@ -8795,26 +5672,16 @@
     </row>
     <row r="78" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B78" s="5">
         <v>7</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
       <c r="H78" s="11"/>
       <c r="I78" s="11"/>
       <c r="J78" s="11"/>
@@ -8825,14 +5692,12 @@
     </row>
     <row r="79" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B79" s="5">
         <v>8</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="C79" s="5"/>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
       <c r="F79" s="11"/>
@@ -8847,7 +5712,7 @@
     </row>
     <row r="80" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B80" s="5">
         <v>9</v>
@@ -8867,7 +5732,7 @@
     </row>
     <row r="81" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B81" s="5">
         <v>10</v>
@@ -8887,7 +5752,7 @@
     </row>
     <row r="82" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B82" s="5">
         <v>11</v>
@@ -8907,7 +5772,7 @@
     </row>
     <row r="83" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B83" s="5">
         <v>12</v>
@@ -8927,7 +5792,7 @@
     </row>
     <row r="84" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B84" s="5">
         <v>13</v>
@@ -8947,7 +5812,7 @@
     </row>
     <row r="85" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B85" s="5">
         <v>14</v>
@@ -8967,7 +5832,7 @@
     </row>
     <row r="86" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B86" s="5">
         <v>1</v>
@@ -8987,7 +5852,7 @@
     </row>
     <row r="87" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B87" s="5">
         <v>2</v>
@@ -9007,7 +5872,7 @@
     </row>
     <row r="88" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B88" s="5">
         <v>3</v>
@@ -9027,7 +5892,7 @@
     </row>
     <row r="89" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B89" s="5">
         <v>4</v>
@@ -9047,7 +5912,7 @@
     </row>
     <row r="90" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B90" s="5">
         <v>5</v>
@@ -9067,7 +5932,7 @@
     </row>
     <row r="91" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B91" s="5">
         <v>6</v>
@@ -9087,7 +5952,7 @@
     </row>
     <row r="92" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B92" s="5">
         <v>7</v>
@@ -9107,7 +5972,7 @@
     </row>
     <row r="93" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B93" s="5">
         <v>8</v>
@@ -9127,7 +5992,7 @@
     </row>
     <row r="94" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B94" s="5">
         <v>9</v>
@@ -9147,7 +6012,7 @@
     </row>
     <row r="95" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B95" s="5">
         <v>10</v>
@@ -9167,7 +6032,7 @@
     </row>
     <row r="96" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B96" s="5">
         <v>11</v>
@@ -9187,7 +6052,7 @@
     </row>
     <row r="97" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B97" s="5">
         <v>12</v>
@@ -9207,7 +6072,7 @@
     </row>
     <row r="98" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B98" s="5">
         <v>13</v>
@@ -9227,7 +6092,7 @@
     </row>
     <row r="99" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B99" s="5">
         <v>14</v>
@@ -9247,29 +6112,17 @@
     </row>
     <row r="100" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B100" s="13">
         <v>1</v>
       </c>
-      <c r="C100" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G100" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>74</v>
-      </c>
+      <c r="C100" s="14"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
+      <c r="H100" s="14"/>
       <c r="I100" s="14"/>
       <c r="J100" s="15"/>
       <c r="K100" s="14"/>
@@ -9279,20 +6132,14 @@
     </row>
     <row r="101" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B101" s="13">
         <v>2</v>
       </c>
-      <c r="C101" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D101" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E101" s="17" t="s">
-        <v>98</v>
-      </c>
+      <c r="C101" s="14"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
       <c r="F101" s="14"/>
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
@@ -9305,20 +6152,14 @@
     </row>
     <row r="102" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B102" s="13">
         <v>3</v>
       </c>
-      <c r="C102" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E102" s="14" t="s">
-        <v>99</v>
-      </c>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="14"/>
       <c r="F102" s="14"/>
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
@@ -9331,21 +6172,15 @@
     </row>
     <row r="103" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B103" s="13">
         <v>4</v>
       </c>
       <c r="C103" s="14"/>
-      <c r="D103" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F103" s="14" t="s">
-        <v>100</v>
-      </c>
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
@@ -9357,26 +6192,16 @@
     </row>
     <row r="104" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B104" s="13">
         <v>5</v>
       </c>
-      <c r="C104" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D104" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F104" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G104" s="14" t="s">
-        <v>101</v>
-      </c>
+      <c r="C104" s="14"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="14"/>
       <c r="J104" s="15"/>
@@ -9387,23 +6212,15 @@
     </row>
     <row r="105" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B105" s="13">
         <v>6</v>
       </c>
-      <c r="C105" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D105" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>97</v>
-      </c>
+      <c r="C105" s="14"/>
+      <c r="D105" s="17"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
@@ -9415,29 +6232,17 @@
     </row>
     <row r="106" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B106" s="13">
         <v>7</v>
       </c>
-      <c r="C106" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E106" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F106" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G106" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H106" s="14" t="s">
-        <v>105</v>
-      </c>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14"/>
       <c r="I106" s="14"/>
       <c r="J106" s="15"/>
       <c r="K106" s="14"/>
@@ -9447,17 +6252,13 @@
     </row>
     <row r="107" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B107" s="13">
         <v>8</v>
       </c>
-      <c r="C107" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>106</v>
-      </c>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
       <c r="E107" s="14"/>
       <c r="F107" s="14"/>
       <c r="G107" s="14"/>
@@ -9471,17 +6272,13 @@
     </row>
     <row r="108" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B108" s="13">
         <v>9</v>
       </c>
-      <c r="C108" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>107</v>
-      </c>
+      <c r="C108" s="14"/>
+      <c r="D108" s="14"/>
       <c r="E108" s="14"/>
       <c r="F108" s="14"/>
       <c r="G108" s="14"/>
@@ -9495,18 +6292,14 @@
     </row>
     <row r="109" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B109" s="13">
         <v>10</v>
       </c>
       <c r="C109" s="14"/>
-      <c r="D109" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>109</v>
-      </c>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
       <c r="F109" s="14"/>
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
@@ -9519,29 +6312,17 @@
     </row>
     <row r="110" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B110" s="13">
         <v>11</v>
       </c>
-      <c r="C110" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D110" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E110" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F110" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="G110" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H110" s="14" t="s">
-        <v>110</v>
-      </c>
+      <c r="C110" s="14"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
+      <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="15"/>
       <c r="K110" s="14"/>
@@ -9551,26 +6332,16 @@
     </row>
     <row r="111" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B111" s="13">
         <v>12</v>
       </c>
-      <c r="C111" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E111" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F111" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G111" s="14" t="s">
-        <v>108</v>
-      </c>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="14"/>
       <c r="J111" s="15"/>
@@ -9581,23 +6352,15 @@
     </row>
     <row r="112" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B112" s="13">
         <v>13</v>
       </c>
-      <c r="C112" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D112" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E112" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F112" s="17" t="s">
-        <v>112</v>
-      </c>
+      <c r="C112" s="17"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="17"/>
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="17"/>
@@ -9609,20 +6372,14 @@
     </row>
     <row r="113" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B113" s="13">
         <v>14</v>
       </c>
-      <c r="C113" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D113" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E113" s="14" t="s">
-        <v>113</v>
-      </c>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
       <c r="F113" s="14"/>
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
@@ -9635,17 +6392,13 @@
     </row>
     <row r="114" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B114" s="13">
         <v>15</v>
       </c>
-      <c r="C114" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D114" s="14" t="s">
-        <v>114</v>
-      </c>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
       <c r="E114" s="14"/>
       <c r="F114" s="14"/>
       <c r="G114" s="14"/>
@@ -9659,20 +6412,14 @@
     </row>
     <row r="115" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B115" s="13">
         <v>16</v>
       </c>
-      <c r="C115" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E115" s="14" t="s">
-        <v>115</v>
-      </c>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
       <c r="F115" s="18"/>
       <c r="G115" s="18"/>
       <c r="H115" s="18"/>
@@ -9685,20 +6432,14 @@
     </row>
     <row r="116" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B116" s="13">
         <v>17</v>
       </c>
-      <c r="C116" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D116" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E116" s="14" t="s">
-        <v>116</v>
-      </c>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
       <c r="F116" s="18"/>
       <c r="G116" s="18"/>
       <c r="H116" s="18"/>
@@ -9711,20 +6452,14 @@
     </row>
     <row r="117" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B117" s="13">
         <v>18</v>
       </c>
-      <c r="C117" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="D117" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E117" s="19" t="s">
-        <v>117</v>
-      </c>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
       <c r="F117" s="14"/>
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
@@ -9737,26 +6472,16 @@
     </row>
     <row r="118" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B118" s="13">
         <v>19</v>
       </c>
-      <c r="C118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F118" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="G118" s="14" t="s">
-        <v>118</v>
-      </c>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
       <c r="H118" s="18"/>
       <c r="I118" s="14"/>
       <c r="J118" s="15"/>
@@ -9767,29 +6492,17 @@
     </row>
     <row r="119" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B119" s="13">
         <v>20</v>
       </c>
-      <c r="C119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G119" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H119" s="14" t="s">
-        <v>119</v>
-      </c>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
       <c r="I119" s="14"/>
       <c r="J119" s="15"/>
       <c r="K119" s="14"/>
@@ -9799,17 +6512,13 @@
     </row>
     <row r="120" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B120" s="7">
         <v>1</v>
       </c>
-      <c r="C120" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>121</v>
-      </c>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
       <c r="E120" s="16"/>
       <c r="F120" s="16"/>
       <c r="G120" s="16"/>
@@ -9823,20 +6532,14 @@
     </row>
     <row r="121" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B121" s="20">
         <v>2</v>
       </c>
-      <c r="C121" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D121" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E121" s="20" t="s">
-        <v>122</v>
-      </c>
+      <c r="C121" s="20"/>
+      <c r="D121" s="20"/>
+      <c r="E121" s="20"/>
       <c r="F121" s="14"/>
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
@@ -9849,17 +6552,13 @@
     </row>
     <row r="122" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B122" s="7">
         <v>3</v>
       </c>
-      <c r="C122" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D122" s="18" t="s">
-        <v>124</v>
-      </c>
+      <c r="C122" s="18"/>
+      <c r="D122" s="18"/>
       <c r="E122" s="14"/>
       <c r="F122" s="14"/>
       <c r="G122" s="14"/>
@@ -9873,20 +6572,14 @@
     </row>
     <row r="123" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B123" s="20">
         <v>4</v>
       </c>
-      <c r="C123" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>125</v>
-      </c>
+      <c r="C123" s="14"/>
+      <c r="D123" s="14"/>
+      <c r="E123" s="14"/>
       <c r="F123" s="14"/>
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
@@ -9899,20 +6592,14 @@
     </row>
     <row r="124" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B124" s="7">
         <v>5</v>
       </c>
-      <c r="C124" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>116</v>
-      </c>
+      <c r="C124" s="14"/>
+      <c r="D124" s="14"/>
+      <c r="E124" s="14"/>
       <c r="F124" s="14"/>
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
@@ -9925,17 +6612,13 @@
     </row>
     <row r="125" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B125" s="20">
         <v>6</v>
       </c>
-      <c r="C125" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D125" s="14" t="s">
-        <v>126</v>
-      </c>
+      <c r="C125" s="14"/>
+      <c r="D125" s="14"/>
       <c r="E125" s="14"/>
       <c r="F125" s="14"/>
       <c r="G125" s="14"/>
@@ -9949,7 +6632,7 @@
     </row>
     <row r="126" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B126" s="7">
         <v>7</v>
@@ -9969,7 +6652,7 @@
     </row>
     <row r="127" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B127" s="20">
         <v>8</v>
@@ -9989,17 +6672,13 @@
     </row>
     <row r="128" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B128" s="7">
         <v>9</v>
       </c>
-      <c r="C128" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D128" s="21" t="s">
-        <v>127</v>
-      </c>
+      <c r="C128" s="14"/>
+      <c r="D128" s="21"/>
       <c r="E128" s="14"/>
       <c r="F128" s="14"/>
       <c r="G128" s="14"/>
@@ -10013,7 +6692,7 @@
     </row>
     <row r="129" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B129" s="20">
         <v>10</v>
@@ -10033,16 +6712,14 @@
     </row>
     <row r="130" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B130" s="7">
         <v>11</v>
       </c>
       <c r="C130" s="22"/>
       <c r="D130" s="22"/>
-      <c r="E130" s="14" t="s">
-        <v>128</v>
-      </c>
+      <c r="E130" s="14"/>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
@@ -10055,7 +6732,7 @@
     </row>
     <row r="131" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B131" s="20">
         <v>12</v>
@@ -10075,7 +6752,7 @@
     </row>
     <row r="132" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B132" s="7">
         <v>13</v>
@@ -10095,7 +6772,7 @@
     </row>
     <row r="133" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B133" s="20">
         <v>14</v>
@@ -10115,14 +6792,12 @@
     </row>
     <row r="134" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="B134" s="7">
         <v>15</v>
       </c>
-      <c r="C134" s="23" t="s">
-        <v>129</v>
-      </c>
+      <c r="C134" s="23"/>
       <c r="D134" s="14"/>
       <c r="E134" s="14"/>
       <c r="F134" s="14"/>
